--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_game_world_info[游戏世界信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_game_world_info[游戏世界信息].xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="9.375" customWidth="1" style="1" min="2" max="2"/>
@@ -1086,17 +1086,22 @@
           <t>unlock_id_speed2</t>
         </is>
       </c>
-      <c r="H1" s="0" t="inlineStr">
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>unlock_id_speed0</t>
+        </is>
+      </c>
+      <c r="I1" s="0" t="inlineStr">
         <is>
           <t>map_pos</t>
         </is>
       </c>
-      <c r="I1" s="0" t="inlineStr">
+      <c r="J1" s="0" t="inlineStr">
         <is>
           <t>name[language]</t>
         </is>
       </c>
-      <c r="J1" s="0" t="inlineStr">
+      <c r="K1" s="0" t="inlineStr">
         <is>
           <t>remark</t>
         </is>
@@ -1138,17 +1143,22 @@
           <t>long</t>
         </is>
       </c>
-      <c r="H2" s="0" t="inlineStr">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="I2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="I2" s="0" t="inlineStr">
+      <c r="J2" s="0" t="inlineStr">
         <is>
           <t>long</t>
         </is>
       </c>
-      <c r="J2" s="0" t="inlineStr">
+      <c r="K2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -1190,17 +1200,22 @@
           <t>解锁ID-征服模式-2倍速游戏起始ID</t>
         </is>
       </c>
-      <c r="H3" s="0" t="inlineStr">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>解锁ID-征服模式-0倍速游戏起始ID</t>
+        </is>
+      </c>
+      <c r="I3" s="0" t="inlineStr">
         <is>
           <t>地图坐标</t>
         </is>
       </c>
-      <c r="I3" s="0" t="inlineStr">
+      <c r="J3" s="0" t="inlineStr">
         <is>
           <t>名字</t>
         </is>
       </c>
-      <c r="J3" s="0" t="inlineStr">
+      <c r="K3" s="0" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -1222,18 +1237,21 @@
       <c r="F4" s="0" t="n">
         <v>100310130</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" s="0" t="n">
         <v>100310140</v>
       </c>
-      <c r="H4" s="0" t="inlineStr">
+      <c r="H4" t="n">
+        <v>100310150</v>
+      </c>
+      <c r="I4" s="0" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="I4" s="0" t="n">
+      <c r="J4" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="J4" s="0" t="inlineStr">
+      <c r="K4" s="0" t="inlineStr">
         <is>
           <t>剑与魔法</t>
         </is>
@@ -1255,18 +1273,21 @@
       <c r="F5" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="0" t="inlineStr">
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="0" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="I5" s="0" t="n">
+      <c r="J5" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="J5" s="0" t="inlineStr">
+      <c r="K5" s="0" t="inlineStr">
         <is>
           <t>虚空魔界</t>
         </is>
@@ -1288,18 +1309,21 @@
       <c r="F6" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="0" t="inlineStr">
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="0" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="I6" s="0" t="n">
+      <c r="J6" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="J6" s="0" t="inlineStr">
+      <c r="K6" s="0" t="inlineStr">
         <is>
           <t>刀与剑</t>
         </is>
@@ -1321,18 +1345,21 @@
       <c r="F7" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="0" t="inlineStr">
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="0" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="I7" s="0" t="n">
+      <c r="J7" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="J7" s="0" t="inlineStr">
+      <c r="K7" s="0" t="inlineStr">
         <is>
           <t>魔法世界</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_game_world_info[游戏世界信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_game_world_info[游戏世界信息].xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="9.375" customWidth="1" style="1" min="2" max="2"/>
@@ -1086,22 +1086,27 @@
           <t>unlock_id_speed2</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="0" t="inlineStr">
         <is>
           <t>unlock_id_speed0</t>
         </is>
       </c>
-      <c r="I1" s="0" t="inlineStr">
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>unlock_id_challenge_hundred</t>
+        </is>
+      </c>
+      <c r="J1" s="0" t="inlineStr">
         <is>
           <t>map_pos</t>
         </is>
       </c>
-      <c r="J1" s="0" t="inlineStr">
+      <c r="K1" s="0" t="inlineStr">
         <is>
           <t>name[language]</t>
         </is>
       </c>
-      <c r="K1" s="0" t="inlineStr">
+      <c r="L1" s="0" t="inlineStr">
         <is>
           <t>remark</t>
         </is>
@@ -1143,22 +1148,27 @@
           <t>long</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="0" t="inlineStr">
         <is>
           <t>long</t>
         </is>
       </c>
-      <c r="I2" s="0" t="inlineStr">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="J2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J2" s="0" t="inlineStr">
+      <c r="K2" s="0" t="inlineStr">
         <is>
           <t>long</t>
         </is>
       </c>
-      <c r="K2" s="0" t="inlineStr">
+      <c r="L2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -1200,22 +1210,27 @@
           <t>解锁ID-征服模式-2倍速游戏起始ID</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="0" t="inlineStr">
         <is>
           <t>解锁ID-征服模式-0倍速游戏起始ID</t>
         </is>
       </c>
-      <c r="I3" s="0" t="inlineStr">
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>解锁ID-挑战100勇士-难度起始ID</t>
+        </is>
+      </c>
+      <c r="J3" s="0" t="inlineStr">
         <is>
           <t>地图坐标</t>
         </is>
       </c>
-      <c r="J3" s="0" t="inlineStr">
+      <c r="K3" s="0" t="inlineStr">
         <is>
           <t>名字</t>
         </is>
       </c>
-      <c r="K3" s="0" t="inlineStr">
+      <c r="L3" s="0" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -1240,18 +1255,21 @@
       <c r="G4" s="0" t="n">
         <v>100310140</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" s="0" t="n">
         <v>100310150</v>
       </c>
-      <c r="I4" s="0" t="inlineStr">
+      <c r="I4" t="n">
+        <v>100310160</v>
+      </c>
+      <c r="J4" s="0" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="J4" s="0" t="n">
+      <c r="K4" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="K4" s="0" t="inlineStr">
+      <c r="L4" s="0" t="inlineStr">
         <is>
           <t>剑与魔法</t>
         </is>
@@ -1276,18 +1294,21 @@
       <c r="G5" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="0" t="inlineStr">
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="0" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="J5" s="0" t="n">
+      <c r="K5" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="K5" s="0" t="inlineStr">
+      <c r="L5" s="0" t="inlineStr">
         <is>
           <t>虚空魔界</t>
         </is>
@@ -1312,18 +1333,21 @@
       <c r="G6" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="0" t="inlineStr">
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="0" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="J6" s="0" t="n">
+      <c r="K6" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="K6" s="0" t="inlineStr">
+      <c r="L6" s="0" t="inlineStr">
         <is>
           <t>刀与剑</t>
         </is>
@@ -1348,18 +1372,21 @@
       <c r="G7" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="I7" s="0" t="inlineStr">
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="0" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="J7" s="0" t="n">
+      <c r="K7" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="K7" s="0" t="inlineStr">
+      <c r="L7" s="0" t="inlineStr">
         <is>
           <t>魔法世界</t>
         </is>
